--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdf6caf4d69f340a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa4ac2658cc94e86"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa4ac2658cc94e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01be95ff9e1c43fa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01be95ff9e1c43fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc7d6df79e74b4cbf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc7d6df79e74b4cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60d478bc9f2e46e4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60d478bc9f2e46e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f243c83513a40d4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f243c83513a40d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rba7c0c91bfc545b7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rba7c0c91bfc545b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24bd53430e974f93"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24bd53430e974f93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52355f05675f4d0e"/>
   </x:sheets>
 </x:workbook>
 </file>
